--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T05:20:25+00:00</t>
+    <t>2026-09-28T10:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:16:57+00:00</t>
+    <t>2026-09-28T10:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:26:56+00:00</t>
+    <t>2026-09-28T11:29:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:29:30+00:00</t>
+    <t>2026-09-28T12:11:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:11:39+00:00</t>
+    <t>2026-09-28T20:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T20:57:11+00:00</t>
+    <t>2026-09-28T21:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T21:01:12+00:00</t>
+    <t>2026-09-30T11:29:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:29:35+00:00</t>
+    <t>2026-10-01T05:55:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,8 +84,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Intention (das „Warum") einer onkologischen Therapielinie bzw. eines Behandlungsabschnitts.
-Verwendet aktuelle SNOMED-CT-Codes aus der Hierarchie `362961001 | Procedure by intent`.
+    <t>Intention (das „Warum") einer onkologischen Behandlungsepisode bzw. eines Behandlungsabschnitts:
+**wozu** behandelt wird.
+Verwendet aktuelle SNOMED-CT-Codes aus der Hierarchie `362981000 | Qualifier value`.
+Nicht hier abgebildet sind **neoadjuvant** und **adjuvant**: Sie beantworten nicht das „Wozu",
+sondern beschreiben die Stellung einer Maßnahme zur Operation — eine neoadjuvante Therapie ist
+in aller Regel kurativ intendiert. Sie sind daher mit der Intention kombinierbar statt zu ihr
+alternativ und stehen in der Kontext-Achse (`onko-service-request-kontext`).
 Als Concept-Display dient der englische SNOMED-Anzeigetext des aktuellen Release (validierbar
 gegen tx.fhir.org); die deutschen Begriffe stehen in den Label-Texten
 des Leitfadens. Extensible gebunden – seltene Sonderintentionen dürfen ergänzt werden.</t>
@@ -116,18 +121,6 @@
   </si>
   <si>
     <t>Palliative intent</t>
-  </si>
-  <si>
-    <t>373847000</t>
-  </si>
-  <si>
-    <t>Neoadjuvant intent</t>
-  </si>
-  <si>
-    <t>373846009</t>
-  </si>
-  <si>
-    <t>Adjuvant - intent</t>
   </si>
   <si>
     <t>399707004</t>
@@ -406,7 +399,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -450,31 +443,15 @@
         <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T05:55:59+00:00</t>
+    <t>2026-10-01T06:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T06:38:06+00:00</t>
+    <t>2026-10-01T08:23:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:23:16+00:00</t>
+    <t>2026-10-01T11:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-intent.xlsx
+++ b/ci-build/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:19:09+00:00</t>
+    <t>2026-10-01T11:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
